--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week08_19Oct.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week08_19Oct.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Reviewed by</t>
   </si>
   <si>
-    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Grow's citizenship action and Festivals-of-Light showcase.  EVIDENCE: showcase photos + EFL: cultural; complete this half-term's rows in the SMSC Evidence Tracker before break.</t>
+    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Grow's citizenship action and Festivals-of-Light showcase.  EVIDENCE: showcase photos + evidence platform: cultural; complete this half-term's rows in the SMSC Evidence Tracker before break.</t>
   </si>
   <si>
     <t xml:space="preserve">Subject</t>
@@ -148,7 +148,7 @@
   </si>
   <si>
     <t xml:space="preserve">Teacher runs the rotation as a site foreman giving live feedback per station; TA photographs each pupil's accurate measure for AQA UAS evidence; logs stay short — numbers, not sentences.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: next task adapted; who needs the method re-modelled shapes grouping and the half-termly plan [NS].</t>
@@ -209,7 +209,7 @@
   </si>
   <si>
     <t xml:space="preserve">TA photographs throughout and supports the clips; teacher hosts the impact-wall debrief; evidence filed with pupils, not about them — celebrate publicly.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: the W7 pitch shapes the W8 real action; outcomes feed APDR and the citizenship ladder [NS].</t>
